--- a/src/dtm_buildsheet/resources/templates/build_sheet_template_v2.xlsx
+++ b/src/dtm_buildsheet/resources/templates/build_sheet_template_v2.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,11 @@
         <fgColor rgb="00C9A84C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEEF6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -141,10 +146,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -548,7 +557,7 @@
           <t>AGENCY / DEPT:</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>SALES REP:</t>
@@ -562,7 +571,7 @@
           <t>PRIMARY CONTACT:</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>QUOTE / ESTIMATE #:</t>
@@ -576,7 +585,7 @@
           <t>PHONE:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>ADDITIONAL INFO:</t>
@@ -590,7 +599,13 @@
           <t>EMAIL:</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>BUILD TYPE:</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -610,7 +625,7 @@
           <t>UNIT ID:</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>UNIT ID:</t>
@@ -624,7 +639,7 @@
           <t>VIN:</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>VIN:</t>
@@ -638,7 +653,7 @@
           <t>YEAR:</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>YEAR:</t>
@@ -652,7 +667,7 @@
           <t>MAKE:</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MAKE:</t>
@@ -666,7 +681,7 @@
           <t>MODEL:</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>MODEL:</t>
@@ -680,7 +695,7 @@
           <t>SUB MODEL:</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>SUB MODEL:</t>
@@ -1403,7 +1418,7 @@
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Interior Light Bar</t>
+          <t>Front Interior Light Bar</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -1613,7 +1628,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>REAR INTERIOR</t>
+          <t>RADAR &amp; THERMAL</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1636,7 @@
       <c r="A71" s="7" t="n"/>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Rear Interior Light Bar</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1634,103 +1649,103 @@
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>RADAR &amp; THERMAL</t>
-        </is>
-      </c>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Front Radar Antenna Mount</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="n"/>
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="9" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Rear Radar Antenna Mount</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="7" t="n"/>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>Front Radar Antenna Mount</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-      <c r="J74" s="7" t="n"/>
-      <c r="K74" s="7" t="n"/>
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Radar Interface Cable (To Camera)</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="n"/>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>Rear Radar Antenna Mount</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Thermal Imager</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
+      <c r="K75" s="7" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="7" t="n"/>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Radar Interface Cable (To Camera)</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Thermal Imager</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-      <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9" t="n"/>
-      <c r="J77" s="9" t="n"/>
-      <c r="K77" s="9" t="n"/>
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Thermal Imager Monitor</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>LIGHT CONTROLLER &amp; ELECTRONICS</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="7" t="n"/>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>Thermal Imager Monitor</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Light Controller</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1743,69 +1758,69 @@
       <c r="J78" s="7" t="n"/>
       <c r="K78" s="7" t="n"/>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>LIGHT CONTROLLER &amp; ELECTRONICS</t>
-        </is>
-      </c>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Control Head</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="9" t="n"/>
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="9" t="n"/>
+      <c r="K79" s="9" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="9" t="n"/>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>Light Controler</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
+      <c r="A80" s="7" t="n"/>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Vehicle interface</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="7" t="n"/>
+      <c r="K80" s="7" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="7" t="n"/>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Control Head</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="n"/>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-      <c r="J81" s="7" t="n"/>
-      <c r="K81" s="7" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="9" t="n"/>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>Vehicle interface</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
-      <c r="H82" s="9" t="n"/>
-      <c r="I82" s="9" t="n"/>
-      <c r="J82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Expansion Module</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="9" t="n"/>
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>PA / SIREN CONTROL</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="7" t="n"/>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Expansion Module</t>
+          <t>Pa Mic</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1818,35 +1833,35 @@
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
     </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>PA / SIREN CONTROL</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="9" t="n"/>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Pa Mic</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="n"/>
-      <c r="K85" s="9" t="n"/>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>Pa Mic Clip</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>RADIO &amp; COMMUNICATIONS</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="7" t="n"/>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Pa Mic Clip</t>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Radio 1</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1859,1378 +1874,1387 @@
       <c r="J86" s="7" t="n"/>
       <c r="K86" s="7" t="n"/>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>RADIO &amp; COMMUNICATIONS</t>
-        </is>
-      </c>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Radio Mic Clip 1</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="9" t="n"/>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="9" t="n"/>
+      <c r="K87" s="9" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="9" t="n"/>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>Radio 1</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
-      <c r="H88" s="9" t="n"/>
-      <c r="I88" s="9" t="n"/>
-      <c r="J88" s="9" t="n"/>
-      <c r="K88" s="9" t="n"/>
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Radio Antenna Cable</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="7" t="n"/>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 1</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>Radio Antenna Top</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="9" t="n"/>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="n"/>
+      <c r="K89" s="9" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="9" t="n"/>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>Radio Antenna Cable</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
-      <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Radio 2</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="7" t="n"/>
+      <c r="K90" s="7" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="7" t="n"/>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>Radio Antenna Top</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Radio Mic Clip 2</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="9" t="n"/>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>Radio 2</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
-      <c r="H92" s="9" t="n"/>
-      <c r="I92" s="9" t="n"/>
-      <c r="J92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="7" t="n"/>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 2</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
-      <c r="I93" s="7" t="n"/>
-      <c r="J93" s="7" t="n"/>
-      <c r="K93" s="7" t="n"/>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Radio Speaker</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+      <c r="J92" s="7" t="n"/>
+      <c r="K92" s="7" t="n"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>CENTER CONSOLE &amp; COMPUTER</t>
         </is>
       </c>
     </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Center Console</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+    </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="9" t="n"/>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>Center Console</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="9" t="n"/>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Special Face Plate 1</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="7" t="n"/>
+      <c r="G95" s="7" t="n"/>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+      <c r="J95" s="7" t="n"/>
+      <c r="K95" s="7" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="7" t="n"/>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Special Face Plate 1</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
-      <c r="K96" s="7" t="n"/>
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Special Face Plate 2</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="9" t="n"/>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="9" t="n"/>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>Special Face Plate 2</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="n"/>
-      <c r="D97" s="9" t="n"/>
-      <c r="E97" s="9" t="n"/>
-      <c r="F97" s="9" t="n"/>
-      <c r="G97" s="9" t="n"/>
-      <c r="H97" s="9" t="n"/>
-      <c r="I97" s="9" t="n"/>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Special Face Plate 3</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="7" t="n"/>
+      <c r="K97" s="7" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="7" t="n"/>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Special Face Plate 3</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
-      <c r="K98" s="7" t="n"/>
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Special Face Plate 4</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="9" t="n"/>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>Special Face Plate 4</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="n"/>
-      <c r="J99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Special Face Plate 5</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="7" t="n"/>
+      <c r="K99" s="7" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="7" t="n"/>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Special Face Plate 5</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="7" t="n"/>
-      <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="7" t="n"/>
-      <c r="J100" s="7" t="n"/>
-      <c r="K100" s="7" t="n"/>
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Special Face Plate 6</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>Special Face Plate 6</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="n"/>
-      <c r="D101" s="9" t="n"/>
-      <c r="E101" s="9" t="n"/>
-      <c r="F101" s="9" t="n"/>
-      <c r="G101" s="9" t="n"/>
-      <c r="H101" s="9" t="n"/>
-      <c r="I101" s="9" t="n"/>
-      <c r="J101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Special Face Plate 7</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="7" t="n"/>
+      <c r="G101" s="7" t="n"/>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="7" t="n"/>
+      <c r="K101" s="7" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="7" t="n"/>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Special Face Plate 7</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="7" t="n"/>
-      <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
-      <c r="J102" s="7" t="n"/>
-      <c r="K102" s="7" t="n"/>
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Arm Rest</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="9" t="n"/>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>Arm Rest</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="n"/>
-      <c r="D103" s="9" t="n"/>
-      <c r="E103" s="9" t="n"/>
-      <c r="F103" s="9" t="n"/>
-      <c r="G103" s="9" t="n"/>
-      <c r="H103" s="9" t="n"/>
-      <c r="I103" s="9" t="n"/>
-      <c r="J103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Motion Attachment</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="7" t="n"/>
+      <c r="G103" s="7" t="n"/>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+      <c r="J103" s="7" t="n"/>
+      <c r="K103" s="7" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="7" t="n"/>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Motion Attachment</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="7" t="n"/>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
-      <c r="J104" s="7" t="n"/>
-      <c r="K104" s="7" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Docking Station</t>
         </is>
       </c>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>PRINTER</t>
         </is>
       </c>
     </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Printer</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="7" t="n"/>
+      <c r="G106" s="7" t="n"/>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+      <c r="J106" s="7" t="n"/>
+      <c r="K106" s="7" t="n"/>
+    </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="7" t="n"/>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="n"/>
-      <c r="E107" s="7" t="n"/>
-      <c r="F107" s="7" t="n"/>
-      <c r="G107" s="7" t="n"/>
-      <c r="H107" s="7" t="n"/>
-      <c r="I107" s="7" t="n"/>
-      <c r="J107" s="7" t="n"/>
-      <c r="K107" s="7" t="n"/>
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Printer Mount</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="9" t="n"/>
+      <c r="H107" s="9" t="n"/>
+      <c r="I107" s="9" t="n"/>
+      <c r="J107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="9" t="n"/>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t>Printer Mount</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="n"/>
-      <c r="D108" s="9" t="n"/>
-      <c r="E108" s="9" t="n"/>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="9" t="n"/>
-      <c r="H108" s="9" t="n"/>
-      <c r="I108" s="9" t="n"/>
-      <c r="J108" s="9" t="n"/>
-      <c r="K108" s="9" t="n"/>
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Printer Power</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+      <c r="J108" s="7" t="n"/>
+      <c r="K108" s="7" t="n"/>
     </row>
     <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="7" t="n"/>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Printer Power</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n"/>
-      <c r="D109" s="7" t="n"/>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="7" t="n"/>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="7" t="n"/>
-      <c r="I109" s="7" t="n"/>
-      <c r="J109" s="7" t="n"/>
-      <c r="K109" s="7" t="n"/>
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Printer USB</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="9" t="n"/>
+      <c r="I109" s="9" t="n"/>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="9" t="n"/>
-      <c r="B110" s="11" t="inlineStr">
-        <is>
-          <t>Printer USB</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="n"/>
-      <c r="D110" s="9" t="n"/>
-      <c r="E110" s="9" t="n"/>
-      <c r="F110" s="9" t="n"/>
-      <c r="G110" s="9" t="n"/>
-      <c r="H110" s="9" t="n"/>
-      <c r="I110" s="9" t="n"/>
-      <c r="J110" s="9" t="n"/>
-      <c r="K110" s="9" t="n"/>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="7" t="n"/>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>12v Aux Ports</t>
         </is>
       </c>
-      <c r="C111" s="7" t="n"/>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
-      <c r="J111" s="7" t="n"/>
-      <c r="K111" s="7" t="n"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="7" t="n"/>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
+      <c r="J110" s="7" t="n"/>
+      <c r="K110" s="7" t="n"/>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>CAMERAS &amp; DVR</t>
         </is>
       </c>
     </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Camera DVR</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="9" t="n"/>
+      <c r="J112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+    </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="9" t="n"/>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>Camera DVR</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="n"/>
-      <c r="D113" s="9" t="n"/>
-      <c r="E113" s="9" t="n"/>
-      <c r="F113" s="9" t="n"/>
-      <c r="G113" s="9" t="n"/>
-      <c r="H113" s="9" t="n"/>
-      <c r="I113" s="9" t="n"/>
-      <c r="J113" s="9" t="n"/>
-      <c r="K113" s="9" t="n"/>
+      <c r="A113" s="7" t="n"/>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Front Camera</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+      <c r="J113" s="7" t="n"/>
+      <c r="K113" s="7" t="n"/>
     </row>
     <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="7" t="n"/>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Front Camera</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="n"/>
-      <c r="D114" s="7" t="n"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="7" t="n"/>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
-      <c r="J114" s="7" t="n"/>
-      <c r="K114" s="7" t="n"/>
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Body Camera Dock</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="9" t="n"/>
+      <c r="H114" s="9" t="n"/>
+      <c r="I114" s="9" t="n"/>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="9" t="n"/>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t>Body Camera Dock</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="n"/>
-      <c r="D115" s="9" t="n"/>
-      <c r="E115" s="9" t="n"/>
-      <c r="F115" s="9" t="n"/>
-      <c r="G115" s="9" t="n"/>
-      <c r="H115" s="9" t="n"/>
-      <c r="I115" s="9" t="n"/>
-      <c r="J115" s="9" t="n"/>
-      <c r="K115" s="9" t="n"/>
+      <c r="A115" s="7" t="n"/>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Rear Seat Camera</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+      <c r="J115" s="7" t="n"/>
+      <c r="K115" s="7" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="7" t="n"/>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>Rear Seat Camera</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="n"/>
-      <c r="D116" s="7" t="n"/>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="7" t="n"/>
-      <c r="G116" s="7" t="n"/>
-      <c r="H116" s="7" t="n"/>
-      <c r="I116" s="7" t="n"/>
-      <c r="J116" s="7" t="n"/>
-      <c r="K116" s="7" t="n"/>
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Rear Camera</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
+      <c r="H116" s="9" t="n"/>
+      <c r="I116" s="9" t="n"/>
+      <c r="J116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="9" t="n"/>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>Rear Camera</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="n"/>
-      <c r="D117" s="9" t="n"/>
-      <c r="E117" s="9" t="n"/>
-      <c r="F117" s="9" t="n"/>
-      <c r="G117" s="9" t="n"/>
-      <c r="H117" s="9" t="n"/>
-      <c r="I117" s="9" t="n"/>
-      <c r="J117" s="9" t="n"/>
-      <c r="K117" s="9" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="7" t="n"/>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>Wireless Mic Charger</t>
         </is>
       </c>
-      <c r="C118" s="7" t="n"/>
-      <c r="D118" s="7" t="n"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="7" t="n"/>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="7" t="n"/>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+      <c r="J117" s="7" t="n"/>
+      <c r="K117" s="7" t="n"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>PARTITIONS &amp; PRISONER AREA</t>
         </is>
       </c>
     </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Front Partition</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="9" t="n"/>
+      <c r="H119" s="9" t="n"/>
+      <c r="I119" s="9" t="n"/>
+      <c r="J119" s="9" t="n"/>
+      <c r="K119" s="9" t="n"/>
+    </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="9" t="n"/>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>Front Partition</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="n"/>
-      <c r="D120" s="9" t="n"/>
-      <c r="E120" s="9" t="n"/>
-      <c r="F120" s="9" t="n"/>
-      <c r="G120" s="9" t="n"/>
-      <c r="H120" s="9" t="n"/>
-      <c r="I120" s="9" t="n"/>
-      <c r="J120" s="9" t="n"/>
-      <c r="K120" s="9" t="n"/>
+      <c r="A120" s="7" t="n"/>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Barrier</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+      <c r="J120" s="7" t="n"/>
+      <c r="K120" s="7" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="7" t="n"/>
-      <c r="B121" s="12" t="inlineStr">
-        <is>
-          <t>Chicago Barrier</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="n"/>
-      <c r="D121" s="7" t="n"/>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="7" t="n"/>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
-      <c r="J121" s="7" t="n"/>
-      <c r="K121" s="7" t="n"/>
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Front Partition Transfer Kit</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="9" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="9" t="n"/>
+      <c r="G121" s="9" t="n"/>
+      <c r="H121" s="9" t="n"/>
+      <c r="I121" s="9" t="n"/>
+      <c r="J121" s="9" t="n"/>
+      <c r="K121" s="9" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="9" t="n"/>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t>Front Partition Transfer Kit</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="9" t="n"/>
-      <c r="E122" s="9" t="n"/>
-      <c r="F122" s="9" t="n"/>
-      <c r="G122" s="9" t="n"/>
-      <c r="H122" s="9" t="n"/>
-      <c r="I122" s="9" t="n"/>
-      <c r="J122" s="9" t="n"/>
-      <c r="K122" s="9" t="n"/>
+      <c r="A122" s="7" t="n"/>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Rear Seat Lights 1</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="7" t="n"/>
+      <c r="G122" s="7" t="n"/>
+      <c r="H122" s="7" t="n"/>
+      <c r="I122" s="7" t="n"/>
+      <c r="J122" s="7" t="n"/>
+      <c r="K122" s="7" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="7" t="n"/>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 1</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="n"/>
-      <c r="D123" s="7" t="n"/>
-      <c r="E123" s="7" t="n"/>
-      <c r="F123" s="7" t="n"/>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
-      <c r="J123" s="7" t="n"/>
-      <c r="K123" s="7" t="n"/>
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Rear Seat Lights 2</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="9" t="n"/>
+      <c r="H123" s="9" t="n"/>
+      <c r="I123" s="9" t="n"/>
+      <c r="J123" s="9" t="n"/>
+      <c r="K123" s="9" t="n"/>
     </row>
     <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="9" t="n"/>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 2</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="n"/>
-      <c r="D124" s="9" t="n"/>
-      <c r="E124" s="9" t="n"/>
-      <c r="F124" s="9" t="n"/>
-      <c r="G124" s="9" t="n"/>
-      <c r="H124" s="9" t="n"/>
-      <c r="I124" s="9" t="n"/>
-      <c r="J124" s="9" t="n"/>
-      <c r="K124" s="9" t="n"/>
+      <c r="A124" s="7" t="n"/>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Rear Seat Cargo Lights</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n"/>
+      <c r="D124" s="7" t="n"/>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="7" t="n"/>
+      <c r="G124" s="7" t="n"/>
+      <c r="H124" s="7" t="n"/>
+      <c r="I124" s="7" t="n"/>
+      <c r="J124" s="7" t="n"/>
+      <c r="K124" s="7" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="7" t="n"/>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>Rear Seat Cargo Lights</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="n"/>
-      <c r="D125" s="7" t="n"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-      <c r="J125" s="7" t="n"/>
-      <c r="K125" s="7" t="n"/>
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Rear Seat Divider</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="9" t="n"/>
+      <c r="H125" s="9" t="n"/>
+      <c r="I125" s="9" t="n"/>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="9" t="n"/>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>Rear Seat Divider</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="n"/>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n"/>
-      <c r="F126" s="9" t="n"/>
-      <c r="G126" s="9" t="n"/>
-      <c r="H126" s="9" t="n"/>
-      <c r="I126" s="9" t="n"/>
-      <c r="J126" s="9" t="n"/>
-      <c r="K126" s="9" t="n"/>
+      <c r="A126" s="7" t="n"/>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Rear Window Bars</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n"/>
+      <c r="D126" s="7" t="n"/>
+      <c r="E126" s="7" t="n"/>
+      <c r="F126" s="7" t="n"/>
+      <c r="G126" s="7" t="n"/>
+      <c r="H126" s="7" t="n"/>
+      <c r="I126" s="7" t="n"/>
+      <c r="J126" s="7" t="n"/>
+      <c r="K126" s="7" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="7" t="n"/>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>Rear Window Bars</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="n"/>
-      <c r="D127" s="7" t="n"/>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="7" t="n"/>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
-      <c r="J127" s="7" t="n"/>
-      <c r="K127" s="7" t="n"/>
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Replacement Rear Seat</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
+      <c r="H127" s="9" t="n"/>
+      <c r="I127" s="9" t="n"/>
+      <c r="J127" s="9" t="n"/>
+      <c r="K127" s="9" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="9" t="n"/>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>Replacement Rear Seat</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="n"/>
-      <c r="D128" s="9" t="n"/>
-      <c r="E128" s="9" t="n"/>
-      <c r="F128" s="9" t="n"/>
-      <c r="G128" s="9" t="n"/>
-      <c r="H128" s="9" t="n"/>
-      <c r="I128" s="9" t="n"/>
-      <c r="J128" s="9" t="n"/>
-      <c r="K128" s="9" t="n"/>
+      <c r="A128" s="7" t="n"/>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Rear Partition</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="7" t="n"/>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
+      <c r="J128" s="7" t="n"/>
+      <c r="K128" s="7" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="7" t="n"/>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>Rear Partition</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="n"/>
-      <c r="D129" s="7" t="n"/>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="7" t="n"/>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="7" t="n"/>
-      <c r="I129" s="7" t="n"/>
-      <c r="J129" s="7" t="n"/>
-      <c r="K129" s="7" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="9" t="n"/>
-      <c r="B130" s="10" t="inlineStr">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>Floor Pan</t>
         </is>
       </c>
-      <c r="C130" s="9" t="n"/>
-      <c r="D130" s="9" t="n"/>
-      <c r="E130" s="9" t="n"/>
-      <c r="F130" s="9" t="n"/>
-      <c r="G130" s="9" t="n"/>
-      <c r="H130" s="9" t="n"/>
-      <c r="I130" s="9" t="n"/>
-      <c r="J130" s="9" t="n"/>
-      <c r="K130" s="9" t="n"/>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="9" t="n"/>
+      <c r="H129" s="9" t="n"/>
+      <c r="I129" s="9" t="n"/>
+      <c r="J129" s="9" t="n"/>
+      <c r="K129" s="9" t="n"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>ARMOR &amp; PROTECTION</t>
         </is>
       </c>
     </row>
+    <row r="131" ht="15" customHeight="1">
+      <c r="A131" s="7" t="n"/>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>Bullet Proof Door Panel(s)</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+      <c r="J131" s="7" t="n"/>
+      <c r="K131" s="7" t="n"/>
+    </row>
     <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="7" t="n"/>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>Bullet Proof Door Panel(s)</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="n"/>
-      <c r="D132" s="7" t="n"/>
-      <c r="E132" s="7" t="n"/>
-      <c r="F132" s="7" t="n"/>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-      <c r="J132" s="7" t="n"/>
-      <c r="K132" s="7" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="9" t="n"/>
-      <c r="B133" s="10" t="inlineStr">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>Bullet Proof Door Window(s)</t>
         </is>
       </c>
-      <c r="C133" s="9" t="n"/>
-      <c r="D133" s="9" t="n"/>
-      <c r="E133" s="9" t="n"/>
-      <c r="F133" s="9" t="n"/>
-      <c r="G133" s="9" t="n"/>
-      <c r="H133" s="9" t="n"/>
-      <c r="I133" s="9" t="n"/>
-      <c r="J133" s="9" t="n"/>
-      <c r="K133" s="9" t="n"/>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
+      <c r="H132" s="9" t="n"/>
+      <c r="I132" s="9" t="n"/>
+      <c r="J132" s="9" t="n"/>
+      <c r="K132" s="9" t="n"/>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>CARGO &amp; STORAGE</t>
         </is>
       </c>
     </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="7" t="n"/>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Storage Compartment</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
+      <c r="E134" s="7" t="n"/>
+      <c r="F134" s="7" t="n"/>
+      <c r="G134" s="7" t="n"/>
+      <c r="H134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
+      <c r="J134" s="7" t="n"/>
+      <c r="K134" s="7" t="n"/>
+    </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="7" t="n"/>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>Storage Compartment</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="n"/>
-      <c r="D135" s="7" t="n"/>
-      <c r="E135" s="7" t="n"/>
-      <c r="F135" s="7" t="n"/>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="7" t="n"/>
-      <c r="I135" s="7" t="n"/>
-      <c r="J135" s="7" t="n"/>
-      <c r="K135" s="7" t="n"/>
+      <c r="A135" s="9" t="n"/>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Cargo Lighting</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="9" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="9" t="n"/>
+      <c r="G135" s="9" t="n"/>
+      <c r="H135" s="9" t="n"/>
+      <c r="I135" s="9" t="n"/>
+      <c r="J135" s="9" t="n"/>
+      <c r="K135" s="9" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="9" t="n"/>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>Cargo Lighting</t>
-        </is>
-      </c>
-      <c r="C136" s="9" t="n"/>
-      <c r="D136" s="9" t="n"/>
-      <c r="E136" s="9" t="n"/>
-      <c r="F136" s="9" t="n"/>
-      <c r="G136" s="9" t="n"/>
-      <c r="H136" s="9" t="n"/>
-      <c r="I136" s="9" t="n"/>
-      <c r="J136" s="9" t="n"/>
-      <c r="K136" s="9" t="n"/>
+      <c r="A136" s="7" t="n"/>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Door Lock Button</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="7" t="n"/>
+      <c r="G136" s="7" t="n"/>
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
+      <c r="J136" s="7" t="n"/>
+      <c r="K136" s="7" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="7" t="n"/>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Door Lock Button</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="n"/>
-      <c r="D137" s="7" t="n"/>
-      <c r="E137" s="7" t="n"/>
-      <c r="F137" s="7" t="n"/>
-      <c r="G137" s="7" t="n"/>
-      <c r="H137" s="7" t="n"/>
-      <c r="I137" s="7" t="n"/>
-      <c r="J137" s="7" t="n"/>
-      <c r="K137" s="7" t="n"/>
-    </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="9" t="n"/>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>Equipment Tray</t>
         </is>
       </c>
-      <c r="C138" s="9" t="n"/>
-      <c r="D138" s="9" t="n"/>
-      <c r="E138" s="9" t="n"/>
-      <c r="F138" s="9" t="n"/>
-      <c r="G138" s="9" t="n"/>
-      <c r="H138" s="9" t="n"/>
-      <c r="I138" s="9" t="n"/>
-      <c r="J138" s="9" t="n"/>
-      <c r="K138" s="9" t="n"/>
-    </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="9" t="n"/>
+      <c r="G137" s="9" t="n"/>
+      <c r="H137" s="9" t="n"/>
+      <c r="I137" s="9" t="n"/>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>GUNLOCKS</t>
         </is>
       </c>
     </row>
+    <row r="139" ht="15" customHeight="1">
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 1</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+      <c r="J139" s="7" t="n"/>
+      <c r="K139" s="7" t="n"/>
+    </row>
     <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="7" t="n"/>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Gunlock 1</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="n"/>
-      <c r="D140" s="7" t="n"/>
-      <c r="E140" s="7" t="n"/>
-      <c r="F140" s="7" t="n"/>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="7" t="n"/>
-      <c r="I140" s="7" t="n"/>
-      <c r="J140" s="7" t="n"/>
-      <c r="K140" s="7" t="n"/>
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Gunlock Bracket 1</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="9" t="n"/>
+      <c r="H140" s="9" t="n"/>
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="9" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="9" t="n"/>
-      <c r="B141" s="11" t="inlineStr">
-        <is>
-          <t>Gunlock Bracket 1</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="n"/>
-      <c r="D141" s="9" t="n"/>
-      <c r="E141" s="9" t="n"/>
-      <c r="F141" s="9" t="n"/>
-      <c r="G141" s="9" t="n"/>
-      <c r="H141" s="9" t="n"/>
-      <c r="I141" s="9" t="n"/>
-      <c r="J141" s="9" t="n"/>
-      <c r="K141" s="9" t="n"/>
+      <c r="A141" s="7" t="n"/>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 2</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="7" t="n"/>
+      <c r="E141" s="7" t="n"/>
+      <c r="F141" s="7" t="n"/>
+      <c r="G141" s="7" t="n"/>
+      <c r="H141" s="7" t="n"/>
+      <c r="I141" s="7" t="n"/>
+      <c r="J141" s="7" t="n"/>
+      <c r="K141" s="7" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="7" t="n"/>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Gunlock 2</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="n"/>
-      <c r="D142" s="7" t="n"/>
-      <c r="E142" s="7" t="n"/>
-      <c r="F142" s="7" t="n"/>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
-      <c r="J142" s="7" t="n"/>
-      <c r="K142" s="7" t="n"/>
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Gunlock Bracket 2</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+      <c r="H142" s="9" t="n"/>
+      <c r="I142" s="9" t="n"/>
+      <c r="J142" s="9" t="n"/>
+      <c r="K142" s="9" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="9" t="n"/>
-      <c r="B143" s="11" t="inlineStr">
-        <is>
-          <t>Gunlock Bracket 2</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="n"/>
-      <c r="D143" s="9" t="n"/>
-      <c r="E143" s="9" t="n"/>
-      <c r="F143" s="9" t="n"/>
-      <c r="G143" s="9" t="n"/>
-      <c r="H143" s="9" t="n"/>
-      <c r="I143" s="9" t="n"/>
-      <c r="J143" s="9" t="n"/>
-      <c r="K143" s="9" t="n"/>
+      <c r="A143" s="7" t="n"/>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 3</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="7" t="n"/>
+      <c r="E143" s="7" t="n"/>
+      <c r="F143" s="7" t="n"/>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="7" t="n"/>
+      <c r="I143" s="7" t="n"/>
+      <c r="J143" s="7" t="n"/>
+      <c r="K143" s="7" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="7" t="n"/>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Gunlock 3</t>
-        </is>
-      </c>
-      <c r="C144" s="7" t="n"/>
-      <c r="D144" s="7" t="n"/>
-      <c r="E144" s="7" t="n"/>
-      <c r="F144" s="7" t="n"/>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
-      <c r="J144" s="7" t="n"/>
-      <c r="K144" s="7" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="9" t="n"/>
-      <c r="B145" s="11" t="inlineStr">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>Gunlock Bracket 3</t>
         </is>
       </c>
-      <c r="C145" s="9" t="n"/>
-      <c r="D145" s="9" t="n"/>
-      <c r="E145" s="9" t="n"/>
-      <c r="F145" s="9" t="n"/>
-      <c r="G145" s="9" t="n"/>
-      <c r="H145" s="9" t="n"/>
-      <c r="I145" s="9" t="n"/>
-      <c r="J145" s="9" t="n"/>
-      <c r="K145" s="9" t="n"/>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>K-9 EQUIPMENT</t>
         </is>
       </c>
     </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="7" t="n"/>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>K-9 Kennel</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n"/>
+      <c r="D146" s="7" t="n"/>
+      <c r="E146" s="7" t="n"/>
+      <c r="F146" s="7" t="n"/>
+      <c r="G146" s="7" t="n"/>
+      <c r="H146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
+      <c r="J146" s="7" t="n"/>
+      <c r="K146" s="7" t="n"/>
+    </row>
     <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="7" t="n"/>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>K-9 Kennel</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="n"/>
-      <c r="D147" s="7" t="n"/>
-      <c r="E147" s="7" t="n"/>
-      <c r="F147" s="7" t="n"/>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="7" t="n"/>
-      <c r="I147" s="7" t="n"/>
-      <c r="J147" s="7" t="n"/>
-      <c r="K147" s="7" t="n"/>
+      <c r="A147" s="9" t="n"/>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>K-9 Heat Alarm/Popper</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="9" t="n"/>
+      <c r="H147" s="9" t="n"/>
+      <c r="I147" s="9" t="n"/>
+      <c r="J147" s="9" t="n"/>
+      <c r="K147" s="9" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="9" t="n"/>
-      <c r="B148" s="10" t="inlineStr">
-        <is>
-          <t>K-9 Heat Alarm/Popper</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="n"/>
-      <c r="D148" s="9" t="n"/>
-      <c r="E148" s="9" t="n"/>
-      <c r="F148" s="9" t="n"/>
-      <c r="G148" s="9" t="n"/>
-      <c r="H148" s="9" t="n"/>
-      <c r="I148" s="9" t="n"/>
-      <c r="J148" s="9" t="n"/>
-      <c r="K148" s="9" t="n"/>
+      <c r="A148" s="7" t="n"/>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>K-9 Control Head</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="n"/>
+      <c r="D148" s="7" t="n"/>
+      <c r="E148" s="7" t="n"/>
+      <c r="F148" s="7" t="n"/>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
+      <c r="J148" s="7" t="n"/>
+      <c r="K148" s="7" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="7" t="n"/>
-      <c r="B149" s="8" t="inlineStr">
-        <is>
-          <t>K-9 Control Head</t>
-        </is>
-      </c>
-      <c r="C149" s="7" t="n"/>
-      <c r="D149" s="7" t="n"/>
-      <c r="E149" s="7" t="n"/>
-      <c r="F149" s="7" t="n"/>
-      <c r="G149" s="7" t="n"/>
-      <c r="H149" s="7" t="n"/>
-      <c r="I149" s="7" t="n"/>
-      <c r="J149" s="7" t="n"/>
-      <c r="K149" s="7" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="9" t="n"/>
-      <c r="B150" s="10" t="inlineStr">
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>K-9 Add-Ons</t>
         </is>
       </c>
-      <c r="C150" s="9" t="n"/>
-      <c r="D150" s="9" t="n"/>
-      <c r="E150" s="9" t="n"/>
-      <c r="F150" s="9" t="n"/>
-      <c r="G150" s="9" t="n"/>
-      <c r="H150" s="9" t="n"/>
-      <c r="I150" s="9" t="n"/>
-      <c r="J150" s="9" t="n"/>
-      <c r="K150" s="9" t="n"/>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
+      <c r="C149" s="9" t="n"/>
+      <c r="D149" s="9" t="n"/>
+      <c r="E149" s="9" t="n"/>
+      <c r="F149" s="9" t="n"/>
+      <c r="G149" s="9" t="n"/>
+      <c r="H149" s="9" t="n"/>
+      <c r="I149" s="9" t="n"/>
+      <c r="J149" s="9" t="n"/>
+      <c r="K149" s="9" t="n"/>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>ELECTRICAL &amp; POWER</t>
         </is>
       </c>
     </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="7" t="n"/>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>Battery Tender</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="n"/>
+      <c r="D151" s="7" t="n"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="7" t="n"/>
+      <c r="H151" s="7" t="n"/>
+      <c r="I151" s="7" t="n"/>
+      <c r="J151" s="7" t="n"/>
+      <c r="K151" s="7" t="n"/>
+    </row>
     <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="7" t="n"/>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>Battery Tender</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="n"/>
-      <c r="D152" s="7" t="n"/>
-      <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" s="7" t="n"/>
-      <c r="K152" s="7" t="n"/>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="9" t="n"/>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>Auto Eject</t>
         </is>
       </c>
-      <c r="C153" s="9" t="n"/>
-      <c r="D153" s="9" t="n"/>
-      <c r="E153" s="9" t="n"/>
-      <c r="F153" s="9" t="n"/>
-      <c r="G153" s="9" t="n"/>
-      <c r="H153" s="9" t="n"/>
-      <c r="I153" s="9" t="n"/>
-      <c r="J153" s="9" t="n"/>
-      <c r="K153" s="9" t="n"/>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="6" t="inlineStr">
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="9" t="n"/>
+      <c r="H152" s="9" t="n"/>
+      <c r="I152" s="9" t="n"/>
+      <c r="J152" s="9" t="n"/>
+      <c r="K152" s="9" t="n"/>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>CONNECTED SYSTEMS</t>
         </is>
       </c>
     </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="7" t="n"/>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Vehicle to Vehicle Sync</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="7" t="n"/>
+      <c r="G154" s="7" t="n"/>
+      <c r="H154" s="7" t="n"/>
+      <c r="I154" s="7" t="n"/>
+      <c r="J154" s="7" t="n"/>
+      <c r="K154" s="7" t="n"/>
+    </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="7" t="n"/>
-      <c r="B155" s="8" t="inlineStr">
-        <is>
-          <t>Vehicle to Vehicle Sync</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="n"/>
-      <c r="D155" s="7" t="n"/>
-      <c r="E155" s="7" t="n"/>
-      <c r="F155" s="7" t="n"/>
-      <c r="G155" s="7" t="n"/>
-      <c r="H155" s="7" t="n"/>
-      <c r="I155" s="7" t="n"/>
-      <c r="J155" s="7" t="n"/>
-      <c r="K155" s="7" t="n"/>
+      <c r="A155" s="9" t="n"/>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Cloud System</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="9" t="n"/>
+      <c r="G155" s="9" t="n"/>
+      <c r="H155" s="9" t="n"/>
+      <c r="I155" s="9" t="n"/>
+      <c r="J155" s="9" t="n"/>
+      <c r="K155" s="9" t="n"/>
     </row>
     <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="9" t="n"/>
-      <c r="B156" s="10" t="inlineStr">
-        <is>
-          <t>Cloud System</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="n"/>
-      <c r="D156" s="9" t="n"/>
-      <c r="E156" s="9" t="n"/>
-      <c r="F156" s="9" t="n"/>
-      <c r="G156" s="9" t="n"/>
-      <c r="H156" s="9" t="n"/>
-      <c r="I156" s="9" t="n"/>
-      <c r="J156" s="9" t="n"/>
-      <c r="K156" s="9" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="7" t="n"/>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="A156" s="7" t="n"/>
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>Remote Start</t>
         </is>
       </c>
-      <c r="C157" s="7" t="n"/>
-      <c r="D157" s="7" t="n"/>
-      <c r="E157" s="7" t="n"/>
-      <c r="F157" s="7" t="n"/>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="7" t="n"/>
-      <c r="I157" s="7" t="n"/>
-      <c r="J157" s="7" t="n"/>
-      <c r="K157" s="7" t="n"/>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
+      <c r="E156" s="7" t="n"/>
+      <c r="F156" s="7" t="n"/>
+      <c r="G156" s="7" t="n"/>
+      <c r="H156" s="7" t="n"/>
+      <c r="I156" s="7" t="n"/>
+      <c r="J156" s="7" t="n"/>
+      <c r="K156" s="7" t="n"/>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>ARGES &amp; SPOTLIGHT</t>
         </is>
       </c>
     </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Arges</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="9" t="n"/>
+      <c r="F158" s="9" t="n"/>
+      <c r="G158" s="9" t="n"/>
+      <c r="H158" s="9" t="n"/>
+      <c r="I158" s="9" t="n"/>
+      <c r="J158" s="9" t="n"/>
+      <c r="K158" s="9" t="n"/>
+    </row>
     <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="9" t="n"/>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>Arges</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="n"/>
-      <c r="D159" s="9" t="n"/>
-      <c r="E159" s="9" t="n"/>
-      <c r="F159" s="9" t="n"/>
-      <c r="G159" s="9" t="n"/>
-      <c r="H159" s="9" t="n"/>
-      <c r="I159" s="9" t="n"/>
-      <c r="J159" s="9" t="n"/>
-      <c r="K159" s="9" t="n"/>
+      <c r="A159" s="7" t="n"/>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>Arges Controller</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n"/>
+      <c r="D159" s="7" t="n"/>
+      <c r="E159" s="7" t="n"/>
+      <c r="F159" s="7" t="n"/>
+      <c r="G159" s="7" t="n"/>
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
+      <c r="J159" s="7" t="n"/>
+      <c r="K159" s="7" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="7" t="n"/>
-      <c r="B160" s="12" t="inlineStr">
-        <is>
-          <t>Arges Controller</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="n"/>
-      <c r="D160" s="7" t="n"/>
-      <c r="E160" s="7" t="n"/>
-      <c r="F160" s="7" t="n"/>
-      <c r="G160" s="7" t="n"/>
-      <c r="H160" s="7" t="n"/>
-      <c r="I160" s="7" t="n"/>
-      <c r="J160" s="7" t="n"/>
-      <c r="K160" s="7" t="n"/>
+      <c r="A160" s="9" t="n"/>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>Arges Mount</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="9" t="n"/>
+      <c r="H160" s="9" t="n"/>
+      <c r="I160" s="9" t="n"/>
+      <c r="J160" s="9" t="n"/>
+      <c r="K160" s="9" t="n"/>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="9" t="n"/>
-      <c r="B161" s="11" t="inlineStr">
-        <is>
-          <t>Arges Mount</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="n"/>
-      <c r="D161" s="9" t="n"/>
-      <c r="E161" s="9" t="n"/>
-      <c r="F161" s="9" t="n"/>
-      <c r="G161" s="9" t="n"/>
-      <c r="H161" s="9" t="n"/>
-      <c r="I161" s="9" t="n"/>
-      <c r="J161" s="9" t="n"/>
-      <c r="K161" s="9" t="n"/>
+      <c r="A161" s="7" t="n"/>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>Photo Eye</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+      <c r="J161" s="7" t="n"/>
+      <c r="K161" s="7" t="n"/>
     </row>
     <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="7" t="n"/>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>Photo Eye</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="n"/>
-      <c r="D162" s="7" t="n"/>
-      <c r="E162" s="7" t="n"/>
-      <c r="F162" s="7" t="n"/>
-      <c r="G162" s="7" t="n"/>
-      <c r="H162" s="7" t="n"/>
-      <c r="I162" s="7" t="n"/>
-      <c r="J162" s="7" t="n"/>
-      <c r="K162" s="7" t="n"/>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>GPD W/ Extention</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="n"/>
-      <c r="D163" s="9" t="n"/>
-      <c r="E163" s="9" t="n"/>
-      <c r="F163" s="9" t="n"/>
-      <c r="G163" s="9" t="n"/>
-      <c r="H163" s="9" t="n"/>
-      <c r="I163" s="9" t="n"/>
-      <c r="J163" s="9" t="n"/>
-      <c r="K163" s="9" t="n"/>
-    </row>
-    <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="6" t="inlineStr">
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>GPD W/ Extension</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="9" t="n"/>
+      <c r="H162" s="9" t="n"/>
+      <c r="I162" s="9" t="n"/>
+      <c r="J162" s="9" t="n"/>
+      <c r="K162" s="9" t="n"/>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>FINISHING &amp; ACCESSORIES</t>
         </is>
       </c>
     </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="7" t="n"/>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Floor Mats</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="n"/>
+      <c r="D164" s="7" t="n"/>
+      <c r="E164" s="7" t="n"/>
+      <c r="F164" s="7" t="n"/>
+      <c r="G164" s="7" t="n"/>
+      <c r="H164" s="7" t="n"/>
+      <c r="I164" s="7" t="n"/>
+      <c r="J164" s="7" t="n"/>
+      <c r="K164" s="7" t="n"/>
+    </row>
     <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="7" t="n"/>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>Floor Mats</t>
-        </is>
-      </c>
-      <c r="C165" s="7" t="n"/>
-      <c r="D165" s="7" t="n"/>
-      <c r="E165" s="7" t="n"/>
-      <c r="F165" s="7" t="n"/>
-      <c r="G165" s="7" t="n"/>
-      <c r="H165" s="7" t="n"/>
-      <c r="I165" s="7" t="n"/>
-      <c r="J165" s="7" t="n"/>
-      <c r="K165" s="7" t="n"/>
+      <c r="A165" s="9" t="n"/>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>Seat Covers</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="n"/>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="9" t="n"/>
+      <c r="H165" s="9" t="n"/>
+      <c r="I165" s="9" t="n"/>
+      <c r="J165" s="9" t="n"/>
+      <c r="K165" s="9" t="n"/>
     </row>
     <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="9" t="n"/>
-      <c r="B166" s="10" t="inlineStr">
-        <is>
-          <t>Seat Covers</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="n"/>
-      <c r="D166" s="9" t="n"/>
-      <c r="E166" s="9" t="n"/>
-      <c r="F166" s="9" t="n"/>
-      <c r="G166" s="9" t="n"/>
-      <c r="H166" s="9" t="n"/>
-      <c r="I166" s="9" t="n"/>
-      <c r="J166" s="9" t="n"/>
-      <c r="K166" s="9" t="n"/>
+      <c r="A166" s="7" t="n"/>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Window Tint</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+      <c r="E166" s="7" t="n"/>
+      <c r="F166" s="7" t="n"/>
+      <c r="G166" s="7" t="n"/>
+      <c r="H166" s="7" t="n"/>
+      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
+      <c r="K166" s="7" t="n"/>
     </row>
     <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="7" t="n"/>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Window Tint</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="n"/>
-      <c r="D167" s="7" t="n"/>
-      <c r="E167" s="7" t="n"/>
-      <c r="F167" s="7" t="n"/>
-      <c r="G167" s="7" t="n"/>
-      <c r="H167" s="7" t="n"/>
-      <c r="I167" s="7" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
+      <c r="A167" s="9" t="n"/>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="n"/>
+      <c r="D167" s="9" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="9" t="n"/>
+      <c r="H167" s="9" t="n"/>
+      <c r="I167" s="9" t="n"/>
+      <c r="J167" s="9" t="n"/>
+      <c r="K167" s="9" t="n"/>
     </row>
     <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="9" t="n"/>
-      <c r="B168" s="10" t="inlineStr">
-        <is>
-          <t>Decals</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="n"/>
-      <c r="D168" s="9" t="n"/>
-      <c r="E168" s="9" t="n"/>
-      <c r="F168" s="9" t="n"/>
-      <c r="G168" s="9" t="n"/>
-      <c r="H168" s="9" t="n"/>
-      <c r="I168" s="9" t="n"/>
-      <c r="J168" s="9" t="n"/>
-      <c r="K168" s="9" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="7" t="n"/>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="A168" s="7" t="n"/>
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>Harness</t>
         </is>
       </c>
-      <c r="C169" s="7" t="n"/>
-      <c r="D169" s="7" t="n"/>
-      <c r="E169" s="7" t="n"/>
-      <c r="F169" s="7" t="n"/>
-      <c r="G169" s="7" t="n"/>
-      <c r="H169" s="7" t="n"/>
-      <c r="I169" s="7" t="n"/>
-      <c r="J169" s="7" t="n"/>
-      <c r="K169" s="7" t="n"/>
-    </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="6" t="inlineStr">
+      <c r="C168" s="7" t="n"/>
+      <c r="D168" s="7" t="n"/>
+      <c r="E168" s="7" t="n"/>
+      <c r="F168" s="7" t="n"/>
+      <c r="G168" s="7" t="n"/>
+      <c r="H168" s="7" t="n"/>
+      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>QUESTIONS / ADDITIONAL NOTES</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="B4:F4"/>
+  <mergeCells count="58">
     <mergeCell ref="H13:K13"/>
+    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A59:K59"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="H12:K12"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A157:K157"/>
+    <mergeCell ref="A169:K169"/>
+    <mergeCell ref="A138:K138"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A70:K70"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A79:K79"/>
-    <mergeCell ref="A146:K146"/>
-    <mergeCell ref="A119:K119"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="G7:K7"/>
+    <mergeCell ref="A153:K153"/>
     <mergeCell ref="H8:K8"/>
-    <mergeCell ref="A87:K87"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A164:K164"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A133:K133"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A118:K118"/>
     <mergeCell ref="H10:K10"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A158:K158"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="H4:K4"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A163:K163"/>
     <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A139:K139"/>
-    <mergeCell ref="A154:K154"/>
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="A55:K55"/>
-    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A151:K151"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A106:K106"/>
-    <mergeCell ref="A131:K131"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A150:K150"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="A134:K134"/>
     <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A43:K43"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A170:K170"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A111:K111"/>
   </mergeCells>
-  <dataValidations count="172">
-    <dataValidation sqref="C16 C17 C18 C19 C21 C22 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41 C42 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C56 C57 C58 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C71 C73 C74 C75 C76 C77 C78 C80 C81 C82 C83 C85 C86 C88 C89 C90 C91 C92 C93 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C107 C108 C109 C110 C111 C113 C114 C115 C116 C117 C118 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C132 C133 C135 C136 C137 C138 C140 C141 C142 C143 C144 C145 C147 C148 C149 C150 C152 C153 C155 C156 C157 C159 C160 C161 C162 C163 C165 C166 C167 C168 C169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="176">
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Patrol,Unmarked,Admin,K-9"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16 C17 C18 C19 C21 C22 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41 C42 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C56 C57 C58 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C71 C72 C73 C74 C75 C76 C78 C79 C80 C81 C83 C84 C86 C87 C88 C89 C90 C91 C92 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C106 C107 C108 C109 C110 C112 C113 C114 C115 C116 C117 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C131 C132 C134 C135 C136 C137 C139 C140 C141 C142 C143 C144 C146 C147 C148 C149 C151 C152 C154 C155 C156 C158 C159 C160 C161 C162 C164 C165 C166 C167 C168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NEW,USED,REUSED,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SETINA,WESTIN,PRO-GARD,GAMBER JOHNSON,TROY,SPECIFY MFG,Westin"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PB400,PB450L,HDX,SPECIFY MODEL,Push Bumper EliteXD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PIT BARS,PB5,PB9,PB10,SPECIFY MODEL,Pit Bar EliteXD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WING WRAPS,PB6,PB8,SPECIFY MODEL,PB10,WING WRAP EliteXD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SETINA,WESTIN,PRO-GARD,GAMBER JOHNSON,TROY,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PB400,PB450L,HDX,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PIT BARS,PB5,PB9,PB10,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"WING WRAPS,PB6,PB8,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E21 E23 E27 E29 E31 E32 E34 E35 E36 E40 E44 E46 E48 E50 E52 E54 E56 E57 E58 E60 E62 E64 E67 E71 E80 E81 E82 E83 E85 E123 E124 E125 E136 E155 E156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E21 E23 E27 E29 E31 E32 E34 E35 E36 E40 E44 E46 E48 E50 E52 E54 E56 E57 E58 E60 E62 E64 E67 E78 E79 E80 E81 E83 E122 E123 E124 E135 E154 E155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WHELEN,SOUNDOFF,SPECIFY MFG"</formula1>
     </dataValidation>
     <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ION,T-ION,2 LAMP TRACER,NFORCE,MPOWER,VXE,SPECIFY MODEL"</formula1>
+      <formula1>"ION,T-ION,2 LAMP TRACER,NFORCE,MPOWER,VXE,SPECIFY MODEL,T-SERIES ION"</formula1>
     </dataValidation>
     <dataValidation sqref="G21 G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TOP TUBE,CENTER PLATE OF PB,GRILL,LOWER GRILL,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="H21 H23 H25 H26 H27 H44 H46 H48 H50 H52 H56 H57 H58 H60 H62 H64 H67 H71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H21 H23 H25 H26 H27 H44 H46 H48 H50 H52 H56 H57 H58 H60 H62 H64 H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Red,Blue,White,Amber,Red/Blue,Red and Blue,Red/White Blue/White,Red/Amber Blue/Amber,Single Color (Specify),Dual Color (Specify),Tri Color (Specify)"</formula1>
     </dataValidation>
     <dataValidation sqref="I21 I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,4,6"</formula1>
     </dataValidation>
-    <dataValidation sqref="J21 J23 J25 J26 J27 J29 J44 J46 J48 J50 J52 J54 J56 J58 J60 J62 J64 J66 J67 J71 J123 J124 J125 J136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STANDARD LENSE,SMOKED LENSE"</formula1>
+    <dataValidation sqref="J21 J23 J25 J26 J27 J29 J44 J46 J48 J50 J52 J54 J56 J58 J60 J62 J64 J66 J67 J122 J123 J124 J135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STANDARD LENS,SMOKED LENS"</formula1>
     </dataValidation>
     <dataValidation sqref="E22 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WHELEN,SOUNDOFF,BEARDED 3D,5-0 FAB (DTM),WESTIN,SPECIFY MFG"</formula1>
@@ -3239,7 +3263,7 @@
       <formula1>"WESTIN 2 LIGHT TUBE,WESTIN 4 LIGHT TUBE,TRACER L BRACKETS X2 PER,UNIVERSAL GRILL BRACKET,SPECIFY BRACKET"</formula1>
     </dataValidation>
     <dataValidation sqref="F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ION,T-ION,2 LAMP TRACER,NFORCE,MPOWER,SPECIFY MODEL"</formula1>
+      <formula1>"ION,T-ION,2 LAMP TRACER,NFORCE,MPOWER,SPECIFY MODEL,T-SERIES ION"</formula1>
     </dataValidation>
     <dataValidation sqref="I23 I25 I26 I27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"2,4,6"</formula1>
@@ -3256,7 +3280,7 @@
     <dataValidation sqref="E26 E33 E45 E47 E49 E51 E53 E61 E63 E65 E68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WHELEN,SOUNDOFF,BEARDED 3D,5-0 FAB (DTM),SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F26 F28 F34 F41 F77 F82 F108 F165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F26 F28 F34 F41 F75 F80 F107 F164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3298,23 +3322,23 @@
     <dataValidation sqref="G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VEHICLE SPECIFIC BRACKET(S),SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="I35 I40 I159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I35 I40 I158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation sqref="G36 G85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G36 G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RIGHT SIDE OF CONSOLE,DRIVERS DOOR,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="E37 E86 E89 E93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E37 E84 E87 E91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MFG CLIP,MAGNETIC MIC"</formula1>
     </dataValidation>
     <dataValidation sqref="E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NOVA,SHO-ME,3M,GTT,SPECIFY MFG"</formula1>
     </dataValidation>
     <dataValidation sqref="G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"IN LIGHT BAR,UPPER WINDSHIELD,ON DASH,IN GRILL,SPECIFY LICATION"</formula1>
+      <formula1>"IN LIGHT BAR,UPPER WINDSHIELD,IN GRILL,SPECIFY LOCATION,CENTER OF DASH"</formula1>
     </dataValidation>
     <dataValidation sqref="J39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STANDARD LENSE,VISABLE LIGHT FILTER"</formula1>
+      <formula1>"STANDARD LENS,VISABLE LIGHT FILTER"</formula1>
     </dataValidation>
     <dataValidation sqref="F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"3"" ROUND(S),6"" ROUND,SPECIFY MODEL"</formula1>
@@ -3328,7 +3352,7 @@
     <dataValidation sqref="E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CRADLE POINT,SIERRA WIRELESS,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="G41 G88 G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G41 G86 G90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FRONT OF PARTITION,ON EQUIPMENT TRAY,SPECIFY LOCATION"</formula1>
     </dataValidation>
     <dataValidation sqref="F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3370,14 +3394,14 @@
     <dataValidation sqref="I57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,4,6,8,FULL BAR,HALF BAR"</formula1>
     </dataValidation>
-    <dataValidation sqref="F58 F71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RST,XLP,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F60 F62 F64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ION,T-SERIES,MEGA T-SERIES,MINI T-SERIES,M-POWER,TRACER 5 LAMP,VXE,VERTEX,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G60 G62 G64 G67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"UPPER REAR WINDOW,ON TAILGATE/LIFTGATE,ABOVE LICENSE PLATE,ON SPECIFIC BRACKET,PILLARS,LOWER LIFTGATE LIP,UNDER TAILGATE,TAIL LIGHTS,REAR BUMPER,SPECIFY LOCATION"</formula1>
+    <dataValidation sqref="G60 G62 G64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"UPPER REAR WINDOW,ON TAILGATE/LIFTGATE,ABOVE LICENSE PLATE,ON SPECIFIC BRACKET,PILLARS,LOWER LIFTGATE LIP,UNDER TAILGATE,TAIL LIGHTS,REAR BUMPER,SPECIFY LOCATION,LICENSE PLATE BRACKET"</formula1>
     </dataValidation>
     <dataValidation sqref="F61 F63 F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LICENSE PLATE BRACKET,L BRACKET,GROMMET MOUNT,TWIST LOCK ADAPTOR,SPECIFY BRACKET"</formula1>
@@ -3394,325 +3418,331 @@
     <dataValidation sqref="F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ION,T-SERIES,MEGA T-SERIES,MINI T-SERIES,M-POWER,VXE,VERTEX,SPECIFY MODEL"</formula1>
     </dataValidation>
+    <dataValidation sqref="G67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"UPPER REAR WINDOW,ON TAILGATE/LIFTGATE,ABOVE LICENSE PLATE,ON SPECIFIC BRACKET,PILLARS,LOWER LIFTGATE LIP,UNDER TAILGATE,TAIL LIGHTS,REAR BUMPER,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="F68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L BRACKET,GROMMET MOUNT,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FLASHED WITH CORE,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="E73 E74 E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E71 E72 E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STALKER,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DSR,DSR 2X,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G73 G78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G71 G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON DASH,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="F74 F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F72 F73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOW A BRACKET,HIGH A BRACKET,DUAL SWIVEL BRACKET,VEHICLE SPECIFIC BRACKET,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DRIVER SIDE DASH,SPECIFY LOCATION"</formula1>
     </dataValidation>
+    <dataValidation sqref="G73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"DRIVER SIDE PILLAR,SPECIFY LOCATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NIGHT RIDE,SPECIFY MFG"</formula1>
+    </dataValidation>
     <dataValidation sqref="G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"DRIVER SIDE PILLAR,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NIGHT RIDE,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SPOT LIGHT MOUNT,DRIVER FENDER MOUNT,PASS FENDER MOUNT,LIGHT BAR MOUNT,SPECIFY LOCATION"</formula1>
     </dataValidation>
+    <dataValidation sqref="F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"DIRECT TO COMPUTER,7"" SCREEN,8"" SCREEN,9"" SCREEN,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="F78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"DIRECT TO COMPUTER,7"" SCREEN,8"" SCREEN,9"" SCREEN,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CORE,BLUEPRINT,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G80 G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G78 G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON EQUIPMENT TRAY,SPECIFY LOCATION"</formula1>
     </dataValidation>
+    <dataValidation sqref="F79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CCTL5,CCTL6,CCTL7,CCTL8,CCTL9,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"IN CENTER CONSOLE,RIGHT SIDE OF CONSOLE,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="F81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CCTL5,CCTL6,CCTL7,CCTL8,CCTL9,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"IN CENTER CONSOLE,RIGHT SIDE OF CONSOLE,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CEM8,CEM16,CEM24,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="E88 E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E86 E90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MOTOROLA,KENWOOD,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F88 F92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F86 F90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ALL IN ONE UNIT,SPLIT UNIT,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G89 G91 G93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G87 G91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON DASH,RIGHT SIDE OF CONSOLE,LEFT SIDE OF CONSOLE,TOP PLATE OF CONSOLE,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="G90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"REAR LEFT ROOF,LEFT CARGO WINDOW,RIGHT CARGO WINDOW,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E91 E133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LEFT CARGO WINDOW,RIGHT CARGO WINDOW,SPECIFY LOCATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E89 E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WHIP STYLE,CYLINDER STYLE,WINDOW MOUNT,SPECITY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="E95 E96 E97 E98 E99 E100 E101 E102 E103 E104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"REAR LEFT ROOF,LEFT CARGO WINDOW,RIGHT CARGO WINDOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E94 E95 E96 E97 E98 E99 E100 E101 E102 E103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GAMBER JOHNSON,HAVIS,TROY,SPECIFY MFG"</formula1>
     </dataValidation>
+    <dataValidation sqref="F94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"VEHICLE SPECIFIC,UNIVERSAL,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="F95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"VEHICLE SPECIFIC,UNIVERSAL,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CORE CONTROL HEAD,MOTORAOLA XTL,WATCHGUARD DVR,ARGES CONTROL HEAD,3.5"" POCKET,6"" POCKET,ACE K-9,SWITCH PLATE (SPECIFY),CUP HOLDERS,FACTORY COMPONANT RELOCATION PLATE,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="F97 F98 F99 F100 F101 F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F96 F97 F98 F99 F100 F101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CORE CONTROL HEAD,MOTORAOLA XTL,WATCHGUARD DVR,ARGES CONTROL HEAD,3.5"" POCKET,6"" POCKET,ACE K-9,SWITCH PLATE (SPECIFY),SPECIFY MODEL"</formula1>
     </dataValidation>
+    <dataValidation sqref="F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STANDARD ARM REST,PRINTER ARM REST,SIDE ARM REST,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="F103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STANDARD ARM REST,PRINTER ARM REST,SIDE ARM REST,SPECIFY MODEL"</formula1>
+      <formula1>"9"" MONGOOSE,9"" XE,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"MOUNTED TO CONSOLE,MOUNTED TO PEDESTAL,SPECIFY LOACTION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GAMBER JOHNSON,HAVIS,SPECIFY"</formula1>
     </dataValidation>
     <dataValidation sqref="F104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"9"" MONGOOSE,9"" XE,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"MOUNTED TO CONSOLE,MOUNTED TO PEDESTAL,SPECIFY LOACTION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"GAMBER JOHNSON,HAVIS,SPECIFY"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SPECIFY DOCK,SPECIFY CRADLE"</formula1>
     </dataValidation>
+    <dataValidation sqref="E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"BROTHER,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PJ-822,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PRINTER ARMREST MOUNT,IN CONSOLE,HEADREST MOUNT,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"BROTHER,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PJ-822,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PRINTER ARMREST MOUNT,IN CONSOLE,HEADREST MOUNT,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GAMBER JOHNSON,HAVIS,PATROL PC,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="E111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SHO-ME,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"USB TYPE A,USB TYPE C,CIGERETTE LIGHTER STYLE,MULTI STYLE BLOCK,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RIGHT SIDE ON CONSOLE,IN FACEPLATE,BACK OF CONSOLE,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="I111 I123 I124 I125 I136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I110 I122 I123 I124 I135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation sqref="E113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"AXON,MOTOTOLA,WATCHGUARD,10-8,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FLEET 3,M500,4RE,FLEET 2,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON FRONT PARTITION,ON EQUIPMENT TRAY,IN CENTER CONSOILE,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="G115 G118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G114 G117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASSENGER SIDE VISOR,ON CENTER CONSOLE,IN GUNLOCK POCKET,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="G116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON DRIVER SIDE HEADLINER,CENTER OF PARTITION,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="E120 E126 E127 E128 E129 E130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E119 E125 E126 E127 E128 E129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SETINA,PRO-GARD,TROY,GAMBER JOHNSON,SPECIFY MFG"</formula1>
     </dataValidation>
+    <dataValidation sqref="F119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FULL PARTITION,SINGLE PRISIONER,FULL XL PARTITION,PASSENGER SIDE XL PARTITION,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="F120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FULL PARTITION,SINGLE PRISIONER,FULL XL PARTITION,PASSENGER SIDE XL PARTITION,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STEEL,POLY,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="F123 F124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F122 F123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"3"" ROUND,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G123 G124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G122 G123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOWER KICK PANEL(S),HEADLINER,ON FRONT PARTITION,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="H123 H124 H125 H136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H122 H123 H124 H135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RED,WHITE,BLUE,RED/WHITE,BLUE WHITE,SPECIFY COLOR(S)"</formula1>
     </dataValidation>
-    <dataValidation sqref="F125 F136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F124 F135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"3"" ROUND,T-SERIES,MEGA T-SERIES,6"" ROUND,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HEADLINER,UNDER SHELF,HEADLINER AND UNDER SHELF,SPECIFY LOCATION(S)"</formula1>
     </dataValidation>
+    <dataValidation sqref="F125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"POLY DIVIDER,CARGO MAXX,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="F126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"POLY DIVIDER,CARGO MAXX,SPECIFY MODEL"</formula1>
+      <formula1>"STEEL VERTICAL,STEEL HORIZONTAL,POLY,POLY TINTED,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STEEL VERTICAL,STEEL HORIZONTAL,POLY,POLY TINTED,SPECIFY MODEL"</formula1>
+      <formula1>"FULL REPLACMENT SEAT W/ CENTER PULL SEAT BELTS,POLY SEAT COVER,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FULL REPLACMENT SEAT W/ CENTER PULL SEAT BELTS,POLY SEAT COVER,SPECIFY MODEL"</formula1>
+      <formula1>"STEEL WINDOW,POLY WINDOW,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STEEL WINDOW,POLY WINDOW,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POLY FLOOR PAN,POLY FLOOR PAN W/ DRAINS"</formula1>
     </dataValidation>
-    <dataValidation sqref="E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ANGEL ARMOR,CLEAR ARMOR,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F132 F133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F131 F132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LEVEL 3A (HANDGUN),LEVEL 3+(RIFLE),SPECIFY MODEL"</formula1>
     </dataValidation>
+    <dataValidation sqref="G131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"DRIVERS DOOR ONLY,DRIVER AND PASSENGER FRONT DOORS,SPECIFY DOOR(S)"</formula1>
+    </dataValidation>
     <dataValidation sqref="G132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"DRIVERS DOOR ONLY,DRIVER AND PASSENGER FRONT DOORS,SPECIFY DOOR(S)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DRIVERS DOOR ONLY,DRIVER AND PASSENGER FRONT DOORS,SPECIFY WINDOW(S)"</formula1>
     </dataValidation>
-    <dataValidation sqref="E135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SETINA,TRUCK VAULT,DECKED,HAVIS,PRO-GARD,GAMBER JOHNSON,5-0 FAB (DTM),WESTIN,AMERICAN ALUMINUM,1ST IN EMERGENCY,ROCKLAND CABINETS,SPECIFY MFG"</formula1>
     </dataValidation>
+    <dataValidation sqref="G135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ON LIFT GATE,HEADLINER,ON LIFTGATE AND HEADLINER,SPECIFY LOCATION(S)"</formula1>
+    </dataValidation>
     <dataValidation sqref="G136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ON LIFT GATE,HEADLINER,ON LIFTGATE AND HEADLINER,SPECIFY LOCATION(S)"</formula1>
+      <formula1>"ON LEFT D-PILLAR,SPECIFY LOCATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SETINA,5-0 FAB (DTM),GAMBER JOHNSON,HAVIS,TRUCK VAULT,TROY,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"EQUIPMENT DRAWER,EQUIPMENT TRAY,EQUIMPENT BOX,REPLACEMENT FLOOR,BOARD,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="G137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ON LEFT D-PILLAR,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SETINA,5-0 FAB (DTM),GAMBER JOHNSON,HAVIS,TRUCK VAULT,TROY,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"EQUIPMENT DRAWER,EQUIPMENT TRAY,EQUIMPENT BOX,REPLACEMENT FLOOR,BOARD,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON REAR PARTITION,UNDER CARGO BOX,PART OF CARGO MAXX,CARGO AREA FLOOR,ON REAR SEAT,IN CONSOLE,SPECIFY LOACTION"</formula1>
     </dataValidation>
+    <dataValidation sqref="E139 E141 E143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SANTA CRUZ,SETINA,BLAC-RAC,PRO-GARD,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F139 F141 F143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SINGLE HANDCUFF,DUAL HANDCUFF,SINGLE SHOT GUN,DUAL SHOT GUN,HANDCUFF AND SHOT GUN,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G139 G141 G143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"OVERHEAD ON FRONT PARTITION,GUN LOCK POCKET,LEFT GUN LOCK POCKET,RIGHT GUN LOCK POCKET,OVER HEAD IN REAR,CARGO AREA MOUNT (SPECIFY),REAR SEAT MOUNT,SINGLE PRISIONER FACING FORWARD,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="E140 E142 E144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SANTA CRUZ,SETINA,BLAC-RAC,PRO-GARD,SPECIFY MFG"</formula1>
+      <formula1>"SETINA,5-0 FAB (DTM),SANTA CRUZ,SPECIFY MFG"</formula1>
     </dataValidation>
     <dataValidation sqref="F140 F142 F144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SINGLE HANDCUFF,DUAL HANDCUFF,SINGLE SHOT GUN,DUAL SHOT GUN,HANDCUFF AND SHOT GUN,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G140 G142 G144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"OVERHEAD ON FRONT PARTITION,GUN LOCK POCKET,LEFT GUN LOCK POCKET,RIGHT GUN LOCK POCKET,OVER HEAD IN REAR,CARGO AREA MOUNT (SPECIFY),REAR SEAT MOUNT,SINGLE PRISIONER FACING FORWARD,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E141 E143 E145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SETINA,5-0 FAB (DTM),SANTA CRUZ,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F141 F143 F145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FRONT OVERHEAD BRACKETS,REAR OVERHEAD BRACKETS,SINGLE T-RAIL,DUAL T-RAIL,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="E147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SETINA,HAVIS,AMERICAN ALUMINUM,SPECIFY MFG"</formula1>
     </dataValidation>
+    <dataValidation sqref="F146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FULL PLATFORM,2/3 1/3 DRIVER EXIT,2/3 1/2 PASS EXIT,ULTIMATE,ULTIMATE II,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E147 E148 E149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ACE K-9,RAY ALLEN,PREIMER K-9,SPECIFY MFG"</formula1>
+    </dataValidation>
     <dataValidation sqref="F147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FULL PLATFORM,2/3 1/3 DRIVER EXIT,2/3 1/2 PASS EXIT,ULTIMATE,ULTIMATE II,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E148 E149 E150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ACE K-9,RAY ALLEN,PREIMER K-9,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HEAT ALARM ONLY,HEAT ALARM AND DOOR POPPER,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="G148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ON FRONT OF K-9 PARTITION,ON EQUIPMEBNT TRAY,SPECIFY LOCATION"</formula1>
     </dataValidation>
-    <dataValidation sqref="G149 G150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G148 G149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"IN CENTER CONSOLE,PASSENGER SIDE VISOR,TOP PLATE OF CONSOLE,RIGHT OF CONSOLE,SPECIFY LOCATION"</formula1>
     </dataValidation>
+    <dataValidation sqref="E151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SCHUMACHER,BATTERY TENDER,KUSSMAUL,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ON EQUIPMENT TRAY,UNDER HOOD,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="E152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SCHUMACHER,BATTERY TENDER,KUSSMAUL,SPECIFY MFG"</formula1>
+      <formula1>"KUSSMAUL,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WATER PROOF,NON-WATER PROOF,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="G152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ON EQUIPMENT TRAY,UNDER HOOD,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"KUSSMAUL,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"WATER PROOF,NON-WATER PROOF,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LEFT FRONT QUARTER PANEL,LEFT REAR QUARTER PANEL,ON BACK RACK,SPECIFY LOCATION"</formula1>
     </dataValidation>
+    <dataValidation sqref="G154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"IN LIGHT BAR,ON CARGO WINDOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"VERIZON ROOF MOUNT,VERIZON WINDOW MOUNT,FIRST NET ROOF MOUNT,FIRST NET WINDOW MOUNT,SPECIFY MODEL"</formula1>
+    </dataValidation>
     <dataValidation sqref="G155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"IN LIGHT BAR,ON CARGO WINDOW"</formula1>
+      <formula1>"ON EQUIPMENT TRAY,FRONT OF PARTITION,SPECIFY LOCATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ARCTI START,SPECIFY MFG"</formula1>
     </dataValidation>
     <dataValidation sqref="F156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"VERIZON ROOF MOUNT,VERIZON WINDOW MOUNT,FIRST NET ROOF MOUNT,FIRST NET WINDOW MOUNT,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ON EQUIPMENT TRAY,FRONT OF PARTITION,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E157" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ARCTI START,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F157" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1 BUTTON 1 WAY,4 BUTTON 1 WAY,1 BUTTON 2 WAY,4 BUTTON 2 WAY,5 BUTTON LCD,SPECIFY"</formula1>
     </dataValidation>
-    <dataValidation sqref="E159 E160 E161 E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E158 E159 E160 E161" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WHELEN,SPECIFY MFG"</formula1>
     </dataValidation>
+    <dataValidation sqref="F158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PRO-FOCUS,SPECIFY MODEL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LEFT FRONT FENDER,RIGHT FRONT FENDER,LEFT AND RIGHT FENDER,LIGHTBAR MOUNT,SPECIFY LOCATION"</formula1>
+    </dataValidation>
     <dataValidation sqref="F159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PRO-FOCUS,SPECIFY MODEL"</formula1>
+      <formula1>"ARGES W/ BAIL BRACKET,ARGES W/ SWIVEL BRACKET,ARGES W/ VERSATILE BAIL BRACKET,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="G159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"LEFT FRONT FENDER,RIGHT FRONT FENDER,LEFT AND RIGHT FENDER,LIGHTBAR MOUNT,SPECIFY LOCATION"</formula1>
+      <formula1>"LEFT ON DASH,IN CENTER CONSOLE,SPECIFY LOCATION"</formula1>
     </dataValidation>
     <dataValidation sqref="F160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ARGES W/ BAIL BRACKET,ARGES W/ SWIVEL BRACKET,ARGES W/ VERSATILE BAIL BRACKET,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"LEFT ON DASH,IN CENTER CONSOLE,SPECIFY LOCATION"</formula1>
+      <formula1>"VEHICLE SPECIFIC MOUNT,LIGHT BAR MOUNT,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F161" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"VEHICLE SPECIFIC MOUNT,LIGHT BAR MOUNT,SPECIFY MODEL"</formula1>
+      <formula1>"CENTER OF DASH,REAR VIEW MIRROR PLASTIC,IN LIGHT BAR,SPECIFY LOCATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GLOBESAT,SPECIFY MFG"</formula1>
     </dataValidation>
     <dataValidation sqref="F162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CENTER OF DASH,REAR VIEW MIRROR PLASTIC,IN LIGHT BAR,SPECIFY LOCATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"GLOBESAT,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CENTER OF DASH,FRONT RIGHT OF DASH,ROOF MOUNTED,SPECIFY LOACTION"</formula1>
     </dataValidation>
+    <dataValidation sqref="E164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WEATHER TECH,HUSKY,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FRONT DRIVER AND PASSENGER,FRONT AND REAR,FRONT REAR AND CARGO,CARGO MAT"</formula1>
+    </dataValidation>
     <dataValidation sqref="E165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"WEATHER TECH,HUSKY,SPECIFY MFG"</formula1>
+      <formula1>"TIGER TOUGH,SPECIFY MFG"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STANDARD,WITH CUSTOM PATCH,SPECIFY MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="G165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FRONT DRIVER AND PASSENGER,FRONT AND REAR,FRONT REAR AND CARGO,CARGO MAT"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TIGER TOUGH,SPECIFY MFG"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STANDARD,WITH CUSTOM PATCH,SPECIFY MODEL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DRIVER ONLY,DRIVER AND PASSENGER,FULL FRONT,FULL REAR,FRONT AND REAR,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="H166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"BLACK,GRAY,SPECIFY COLOR"</formula1>
     </dataValidation>
-    <dataValidation sqref="E167 E169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E166 E168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"5-0 FAB (DTM),SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F167 F169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F166 F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"COMPLETE SQUAD HARNESS,SPECIFY MODEL"</formula1>
     </dataValidation>
-    <dataValidation sqref="E168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ADVANCED GRAPHICS,SPECIFY MFG"</formula1>
     </dataValidation>
-    <dataValidation sqref="F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CUSTOM GRAPHICS ( WORK WITH MFG)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3726,17 +3756,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="13" t="inlineStr">
@@ -3745,125 +3775,145 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="n">
-        <v>1</v>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>INSTALLATION NOTES</t>
+        </is>
       </c>
       <c r="B2" s="15" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="n"/>
+      <c r="A3" s="16" t="n"/>
+      <c r="B3" s="16" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15" t="n"/>
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="17" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="17" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="15" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="14" t="n">
-        <v>7</v>
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>CUSTOMER REQUESTS</t>
+        </is>
       </c>
       <c r="B8" s="15" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="15" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="n">
-        <v>13</v>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>SPECIAL FABRICATION NOTES</t>
+        </is>
       </c>
       <c r="B14" s="15" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="15" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="15" t="n"/>
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="15" t="n"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="14" t="n">
-        <v>19</v>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>DELIVERY REQUIREMENTS</t>
+        </is>
       </c>
       <c r="B20" s="15" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="15" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>FINAL APPROVALS</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
